--- a/01_data/02_output_data/01_bidirectional_results/flow_and_network_data.xlsx
+++ b/01_data/02_output_data/01_bidirectional_results/flow_and_network_data.xlsx
@@ -450,1842 +450,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D91"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Commodity</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Destination</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Flow</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Methane</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>node_0001</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>node_0002_2</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Methane</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>node_0002</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>node_0362</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Methane</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>node_0009</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>node_0012</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Methane</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>node_0011</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>node_0096</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Methane</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>node_0012</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>node_0019</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Methane</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>node_0015</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>node_0016</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Methane</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>node_0016</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>node_0031</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Methane</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>node_0031</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>node_0411</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Methane</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>node_0043</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>node_0069</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Methane</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>node_0049</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>node_0429_1</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Methane</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>node_0061</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>node_0215</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Methane</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>node_0068</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>node_0070</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Methane</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>node_0070</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>node_0071</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Methane</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>node_0071</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>node_0072</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Methane</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>node_0072</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>node_0073</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Methane</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>node_0072</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>node_0451</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Methane</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>node_0073</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>node_0074</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Methane</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>node_0074</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>node_0452</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Methane</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>node_0092</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>node_0110_1</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Methane</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>node_0136</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>node_0208</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Methane</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>node_0137</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>node_0212</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Methane</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>node_0151</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>node_0156</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>1.147961409333333</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Methane</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>node_0152</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>node_0153</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>3.852038590666667</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Methane</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>node_0153</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>node_0158</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>3.852038590666667</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Methane</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>node_0156</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>node_0157_1</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>1.147961409333333</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Methane</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>node_0157</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>node_0158</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>1.147961409333333</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Methane</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>node_0158</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>node_0159</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Methane</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>node_0159</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>node_0160</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Methane</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>node_0160</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>node_0296</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>4.976897231893936</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Methane</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>node_0160</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>node_0297</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>0.02310276810606382</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Methane</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>node_0215</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>node_0365</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Methane</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>node_0234</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>node_0243_1</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>3.875371924000021</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Methane</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>node_0243</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>node_0244</t>
-        </is>
-      </c>
-      <c r="D34" t="n">
-        <v>3.875371924000021</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Methane</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>node_0273</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>node_0584</t>
-        </is>
-      </c>
-      <c r="D35" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Methane</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>node_0307</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>node_0311</t>
-        </is>
-      </c>
-      <c r="D36" t="n">
-        <v>1.124628075999978</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Methane</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>node_0307</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>node_0312_1</t>
-        </is>
-      </c>
-      <c r="D37" t="n">
-        <v>3.875371924000021</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Methane</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>node_0311</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>node_0313</t>
-        </is>
-      </c>
-      <c r="D38" t="n">
-        <v>1.124628075999978</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Methane</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>node_0002_2</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>node_0002</t>
-        </is>
-      </c>
-      <c r="D39" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Methane</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>node_0110_1</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>node_0110</t>
-        </is>
-      </c>
-      <c r="D40" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Methane</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>node_0157_1</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>node_0157</t>
-        </is>
-      </c>
-      <c r="D41" t="n">
-        <v>1.147961409333333</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Methane</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>node_0243_1</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>node_0243</t>
-        </is>
-      </c>
-      <c r="D42" t="n">
-        <v>3.875371924000021</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Methane</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>node_0312_1</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>node_0312</t>
-        </is>
-      </c>
-      <c r="D43" t="n">
-        <v>3.875371924000021</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>Methane</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>node_0429_1</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>node_0429</t>
-        </is>
-      </c>
-      <c r="D44" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Methane</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>node_0098</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>node_0011</t>
-        </is>
-      </c>
-      <c r="D45" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>Methane</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>node_0019</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>node_0015</t>
-        </is>
-      </c>
-      <c r="D46" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>Methane</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>node_0212</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>node_0043</t>
-        </is>
-      </c>
-      <c r="D47" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>Methane</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>node_0088</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>node_0043</t>
-        </is>
-      </c>
-      <c r="D48" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>Methane</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>node_0108</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>node_0049</t>
-        </is>
-      </c>
-      <c r="D49" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>Methane</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>node_0429</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>node_0061</t>
-        </is>
-      </c>
-      <c r="D50" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>Methane</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>node_0069</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>node_0068</t>
-        </is>
-      </c>
-      <c r="D51" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>Methane</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>node_0095</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>node_0088</t>
-        </is>
-      </c>
-      <c r="D52" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>Methane</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>node_0411</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>node_0092</t>
-        </is>
-      </c>
-      <c r="D53" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>Methane</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>node_0096</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>node_0095</t>
-        </is>
-      </c>
-      <c r="D54" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>Methane</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>node_0105</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>node_0104</t>
-        </is>
-      </c>
-      <c r="D55" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>Methane</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>node_0452</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>node_0105</t>
-        </is>
-      </c>
-      <c r="D56" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>Methane</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>node_0109_3</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>node_0108</t>
-        </is>
-      </c>
-      <c r="D57" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>Methane</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>node_0110_4</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>node_0109</t>
-        </is>
-      </c>
-      <c r="D58" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>Methane</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>node_0362</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>node_0136</t>
-        </is>
-      </c>
-      <c r="D59" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>Methane</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>node_0208</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>node_0137</t>
-        </is>
-      </c>
-      <c r="D60" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>Methane</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>node_0152</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>node_0151</t>
-        </is>
-      </c>
-      <c r="D61" t="n">
-        <v>1.147961409333333</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>Methane</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>node_0312</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>node_0234</t>
-        </is>
-      </c>
-      <c r="D62" t="n">
-        <v>3.875371924000021</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>Methane</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>node_0245</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>node_0244</t>
-        </is>
-      </c>
-      <c r="D63" t="n">
-        <v>1.124628075999978</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>Methane</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>node_0248</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>node_0245</t>
-        </is>
-      </c>
-      <c r="D64" t="n">
-        <v>1.124628075999978</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>Methane</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>node_0313_2</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>node_0248</t>
-        </is>
-      </c>
-      <c r="D65" t="n">
-        <v>1.124628075999978</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>Methane</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>node_0296</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>node_0273</t>
-        </is>
-      </c>
-      <c r="D66" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>Methane</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>node_0297</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>node_0296</t>
-        </is>
-      </c>
-      <c r="D67" t="n">
-        <v>0.02310276810606382</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>Methane</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>node_0309</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>node_0307</t>
-        </is>
-      </c>
-      <c r="D68" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>Methane</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>node_0584_2</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>node_0309</t>
-        </is>
-      </c>
-      <c r="D69" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>Methane</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>node_0104</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>node_0104_1</t>
-        </is>
-      </c>
-      <c r="D70" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>Methane</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>node_0109</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>node_0109_3</t>
-        </is>
-      </c>
-      <c r="D71" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>Methane</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>node_0110</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>node_0110_4</t>
-        </is>
-      </c>
-      <c r="D72" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>Methane</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>node_0313</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>node_0313_2</t>
-        </is>
-      </c>
-      <c r="D73" t="n">
-        <v>1.124628075999978</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>Methane</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>node_0584</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>node_0584_2</t>
-        </is>
-      </c>
-      <c r="D74" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>Hydrogen</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>node_0078</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>node_0079</t>
-        </is>
-      </c>
-      <c r="D75" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>Hydrogen</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>node_0079</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>node_0240</t>
-        </is>
-      </c>
-      <c r="D76" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>Hydrogen</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>node_0234</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>node_0314_2</t>
-        </is>
-      </c>
-      <c r="D77" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>Hydrogen</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>node_0238</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>node_0242</t>
-        </is>
-      </c>
-      <c r="D78" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>Hydrogen</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>node_0240</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>node_0241</t>
-        </is>
-      </c>
-      <c r="D79" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>Hydrogen</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>node_0080</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>node_0078</t>
-        </is>
-      </c>
-      <c r="D80" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>Hydrogen</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>node_0081</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>node_0080</t>
-        </is>
-      </c>
-      <c r="D81" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>Hydrogen</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>node_0082</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>node_0081</t>
-        </is>
-      </c>
-      <c r="D82" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>Hydrogen</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>node_0083</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>node_0082</t>
-        </is>
-      </c>
-      <c r="D83" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>Hydrogen</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>node_0084</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>node_0083</t>
-        </is>
-      </c>
-      <c r="D84" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>Hydrogen</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>node_0085</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>node_0084</t>
-        </is>
-      </c>
-      <c r="D85" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>Hydrogen</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>node_0086</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>node_0085</t>
-        </is>
-      </c>
-      <c r="D86" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>Hydrogen</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>node_0091</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>node_0086</t>
-        </is>
-      </c>
-      <c r="D87" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>Hydrogen</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>node_0092</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>node_0091</t>
-        </is>
-      </c>
-      <c r="D88" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>Hydrogen</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>node_0093</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>node_0092</t>
-        </is>
-      </c>
-      <c r="D89" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>Hydrogen</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>node_0242</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>node_0234</t>
-        </is>
-      </c>
-      <c r="D90" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>Hydrogen</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>node_0241</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>node_0238</t>
-        </is>
-      </c>
-      <c r="D91" t="n">
-        <v>5</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
